--- a/data/trans_orig/IP07A10-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A10-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>29178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46025</t>
+          <t>45924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33406</t>
+          <t>33439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50757</t>
+          <t>50109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67227</t>
+          <t>66872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91123</t>
+          <t>90323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56942</t>
+          <t>57864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>75457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68048</t>
+          <t>68444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86938</t>
+          <t>86523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130859</t>
+          <t>129681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155789</t>
+          <t>156475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29861</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33493</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53720</t>
+          <t>53562</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46197</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65801</t>
+          <t>66325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56657</t>
+          <t>57686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78406</t>
+          <t>79470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107581</t>
+          <t>108341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137792</t>
+          <t>138437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75932</t>
+          <t>76140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98470</t>
+          <t>99315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78123</t>
+          <t>77765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101384</t>
+          <t>99919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160691</t>
+          <t>162497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192798</t>
+          <t>194980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54632</t>
+          <t>54484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37159</t>
+          <t>36247</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55031</t>
+          <t>56076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77346</t>
+          <t>76911</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103659</t>
+          <t>104046</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79527</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>106554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94390</t>
+          <t>95263</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>121528</t>
+          <t>121789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181738</t>
+          <t>182594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>219024</t>
+          <t>218298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139684</t>
+          <t>139917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167770</t>
+          <t>168441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152043</t>
+          <t>154098</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182171</t>
+          <t>182596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300277</t>
+          <t>301328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342436</t>
+          <t>341890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56023</t>
+          <t>55413</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81082</t>
+          <t>80147</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54556</t>
+          <t>55339</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>78063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117058</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149372</t>
+          <t>149016</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,42 +2491,42 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>6431</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>11317</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>1,7%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11462</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57459</t>
+          <t>58556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78359</t>
+          <t>78559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52341</t>
+          <t>51510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71394</t>
+          <t>71945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115518</t>
+          <t>113909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144181</t>
+          <t>143599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60783</t>
+          <t>60264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82278</t>
+          <t>81117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57140</t>
+          <t>58243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76632</t>
+          <t>77959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122268</t>
+          <t>122770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152826</t>
+          <t>151671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>22405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>29878</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48152</t>
+          <t>49064</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71361</t>
+          <t>71785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62403</t>
+          <t>62111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83673</t>
+          <t>83050</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119499</t>
+          <t>118539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149032</t>
+          <t>149094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64871</t>
+          <t>65965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85967</t>
+          <t>87345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63998</t>
+          <t>64493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85611</t>
+          <t>84442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135508</t>
+          <t>134600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164818</t>
+          <t>165257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,36%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>20987</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36508</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>17233</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32407</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42597</t>
+          <t>42370</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63758</t>
+          <t>64105</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114333</t>
+          <t>115550</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144334</t>
+          <t>144345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120177</t>
+          <t>120449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150044</t>
+          <t>149008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241801</t>
+          <t>244473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282877</t>
+          <t>284061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132069</t>
+          <t>131654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159882</t>
+          <t>161210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>126948</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155970</t>
+          <t>157559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267474</t>
+          <t>265998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309716</t>
+          <t>307420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58264</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76371</t>
+          <t>74989</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105646</t>
+          <t>103894</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67571</t>
+          <t>67837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90533</t>
+          <t>91136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61725</t>
+          <t>61923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84873</t>
+          <t>84114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137908</t>
+          <t>136425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171553</t>
+          <t>168490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72113</t>
+          <t>71167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>93417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>73927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95807</t>
+          <t>95459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149608</t>
+          <t>149240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183252</t>
+          <t>182275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32881</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33970</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54852</t>
+          <t>54511</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54462</t>
+          <t>53860</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74853</t>
+          <t>74270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61213</t>
+          <t>60826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83452</t>
+          <t>83445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120824</t>
+          <t>122655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151566</t>
+          <t>153006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61820</t>
+          <t>62468</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83484</t>
+          <t>83652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67582</t>
+          <t>67603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90207</t>
+          <t>89586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134931</t>
+          <t>136389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166216</t>
+          <t>166766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,36%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>21318</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37564</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28974</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>38170</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59158</t>
+          <t>60198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129212</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159040</t>
+          <t>160442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130224</t>
+          <t>131036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160981</t>
+          <t>160760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268850</t>
+          <t>268613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310988</t>
+          <t>311359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140063</t>
+          <t>139372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169803</t>
+          <t>169610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146957</t>
+          <t>146408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>178309</t>
+          <t>178404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>294019</t>
+          <t>295945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336572</t>
+          <t>341703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>36615</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58222</t>
+          <t>57644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55314</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76458</t>
+          <t>77435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105744</t>
+          <t>109312</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2023 (tasa de respuesta: 99,79%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7561,12 +7561,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67509</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89743</t>
+          <t>88148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97555</t>
+          <t>98705</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122959</t>
+          <t>123477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175016</t>
+          <t>173135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206320</t>
+          <t>205913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51221</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60768</t>
+          <t>59461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72263</t>
+          <t>71723</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102430</t>
+          <t>104656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26814</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91468</t>
+          <t>93605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159546</t>
+          <t>158556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144774</t>
+          <t>145353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186392</t>
+          <t>184671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>252658</t>
+          <t>246203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331230</t>
+          <t>328690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65925</t>
+          <t>66205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143869</t>
+          <t>137930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69616</t>
+          <t>69030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>105285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148864</t>
+          <t>148250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236002</t>
+          <t>241416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>13586</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34984</t>
+          <t>31466</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>41350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167819</t>
+          <t>163831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>238200</t>
+          <t>239073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253476</t>
+          <t>252924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298778</t>
+          <t>300237</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>438980</t>
+          <t>436115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>527234</t>
+          <t>526584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105311</t>
+          <t>105616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183020</t>
+          <t>186935</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9053,82 +9053,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>134263</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>114526</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>157803</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>35,89%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>263567</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>230694</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>325796</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>28,51%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>49,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>134263</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>114487</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>158597</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>263567</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>230908</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>328086</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>32,58%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
